--- a/survey_templates/042_parent_teacher_organization_guidelines_feedback--survey_templates.xlsx
+++ b/survey_templates/042_parent_teacher_organization_guidelines_feedback--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'clear'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Clear'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'confusing'}</t>
+          <t>confusing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Confusing'}</t>
+          <t>Confusing</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_confusing'}</t>
+          <t>somewhat_confusing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Confusing'}</t>
+          <t>Somewhat Confusing</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'0_-_no_clarity'}</t>
+          <t>0_-_no_clarity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '0 - No Clarity'}</t>
+          <t>0 - No Clarity</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_some_clarity'}</t>
+          <t>1_-_some_clarity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '1 - Some Clarity'}</t>
+          <t>1 - Some Clarity</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_a_lot_of_clarity'}</t>
+          <t>2_-_a_lot_of_clarity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '2 - A lot of Clarity'}</t>
+          <t>2 - A lot of Clarity</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'0_-_not_useful'}</t>
+          <t>0_-_not_useful</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '0 - Not Useful'}</t>
+          <t>0 - Not Useful</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_somewhat_useful'}</t>
+          <t>1_-_somewhat_useful</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '1 - Somewhat Useful'}</t>
+          <t>1 - Somewhat Useful</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_very_useful'}</t>
+          <t>2_-_very_useful</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '2 - Very Useful'}</t>
+          <t>2 - Very Useful</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'0_-_not_recommended'}</t>
+          <t>0_-_not_recommended</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '0 - Not Recommended'}</t>
+          <t>0 - Not Recommended</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_somewhat_recommended'}</t>
+          <t>1_-_somewhat_recommended</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '1 - Somewhat Recommended'}</t>
+          <t>1 - Somewhat Recommended</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_very_recommended'}</t>
+          <t>2_-_very_recommended</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '2 - Very Recommended'}</t>
+          <t>2 - Very Recommended</t>
         </is>
       </c>
     </row>
